--- a/artfynd/A 3053-2024 artfynd.xlsx
+++ b/artfynd/A 3053-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3053-2024 artfynd.xlsx
+++ b/artfynd/A 3053-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2677809</v>
+        <v>15283522</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>102019</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,26 +708,31 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1100 m NV Skillerhult, Sm</t>
+          <t>1000 m NV Skillerhult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569195.0183345289</v>
+        <v>569135</v>
       </c>
       <c r="R2" t="n">
-        <v>6303615.883808389</v>
+        <v>6303605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +762,9 @@
           <t>2012-07-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -791,11 +781,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Annan skogsmark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -808,6 +793,248 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>15283523</v>
+      </c>
+      <c r="B3" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1000 m NV Skillerhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>569135</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6303605</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-07-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-07-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ledningsgata</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helena Lager</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2677806</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>1100 m NV Skillerhult, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569195</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6303616</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-07-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ledningsgata</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Annan skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helena Lager</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ekologa /Jonas Wäglind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3053-2024 artfynd.xlsx
+++ b/artfynd/A 3053-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15283522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15283523</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,8 +1050,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2677806</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>